--- a/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP210"/>
+  <dimension ref="A1:BP212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.55</v>
@@ -2658,7 +2658,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.92</v>
@@ -5492,7 +5492,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR23" t="n">
         <v>0.87</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.64</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ27" t="n">
         <v>1</v>
@@ -7672,7 +7672,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR33" t="n">
         <v>0.35</v>
@@ -8762,7 +8762,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR38" t="n">
         <v>1.77</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.83</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.33</v>
@@ -10506,7 +10506,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR46" t="n">
         <v>1.82</v>
@@ -13773,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.64</v>
@@ -13991,7 +13991,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.33</v>
@@ -14212,7 +14212,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR63" t="n">
         <v>1.29</v>
@@ -14430,7 +14430,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR64" t="n">
         <v>1.73</v>
@@ -16828,7 +16828,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR75" t="n">
         <v>1.78</v>
@@ -17043,7 +17043,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.17</v>
@@ -18569,7 +18569,7 @@
         <v>1</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.82</v>
@@ -19008,7 +19008,7 @@
         <v>2</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR85" t="n">
         <v>1.7</v>
@@ -20316,7 +20316,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR91" t="n">
         <v>1.72</v>
@@ -20749,7 +20749,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.08</v>
@@ -21842,7 +21842,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR98" t="n">
         <v>1.8</v>
@@ -22929,7 +22929,7 @@
         <v>1</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.82</v>
@@ -23147,7 +23147,7 @@
         <v>1.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.92</v>
@@ -24240,7 +24240,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR109" t="n">
         <v>1.51</v>
@@ -25548,7 +25548,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR115" t="n">
         <v>1.64</v>
@@ -26635,10 +26635,10 @@
         <v>2</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR120" t="n">
         <v>1.59</v>
@@ -27943,7 +27943,7 @@
         <v>1.17</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.42</v>
@@ -29472,7 +29472,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR133" t="n">
         <v>1.38</v>
@@ -29687,7 +29687,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ134" t="n">
         <v>1.08</v>
@@ -30780,7 +30780,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR139" t="n">
         <v>1.04</v>
@@ -32521,7 +32521,7 @@
         <v>1.13</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.5</v>
@@ -33829,10 +33829,10 @@
         <v>1</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR153" t="n">
         <v>1.56</v>
@@ -34265,7 +34265,7 @@
         <v>0.38</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.83</v>
@@ -36230,7 +36230,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR164" t="n">
         <v>1.34</v>
@@ -36663,7 +36663,7 @@
         <v>0.88</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.09</v>
@@ -37756,7 +37756,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR171" t="n">
         <v>1.57</v>
@@ -38843,7 +38843,7 @@
         <v>1.44</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.33</v>
@@ -39936,7 +39936,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR181" t="n">
         <v>1.52</v>
@@ -41459,7 +41459,7 @@
         <v>1.1</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ188" t="n">
         <v>1</v>
@@ -42116,7 +42116,7 @@
         <v>2</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR191" t="n">
         <v>1.92</v>
@@ -42331,7 +42331,7 @@
         <v>0.9</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ192" t="n">
         <v>0.82</v>
@@ -43203,7 +43203,7 @@
         <v>1.4</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.17</v>
@@ -43642,7 +43642,7 @@
         <v>2</v>
       </c>
       <c r="AQ198" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR198" t="n">
         <v>1.46</v>
@@ -46334,6 +46334,442 @@
       </c>
       <c r="BP210" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>8206448</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>46081.625</v>
+      </c>
+      <c r="F211" t="n">
+        <v>24</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Angers SCO</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>2</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>2</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>['57', '62']</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R211" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S211" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="T211" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U211" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V211" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X211" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>8206453</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>46081.71180555555</v>
+      </c>
+      <c r="F212" t="n">
+        <v>24</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>1</v>
+      </c>
+      <c r="N212" t="n">
+        <v>1</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>7</v>
+      </c>
+      <c r="R212" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="S212" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U212" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V212" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="W212" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X212" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
@@ -46712,13 +46712,13 @@
         <v>9</v>
       </c>
       <c r="AW212" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX212" t="n">
         <v>13</v>
       </c>
       <c r="AY212" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ212" t="n">
         <v>22</v>

--- a/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP212"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.08</v>
@@ -3312,7 +3312,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR13" t="n">
         <v>1.36</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.33</v>
@@ -3966,7 +3966,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.09</v>
@@ -4838,7 +4838,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
         <v>2.04</v>
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.42</v>
@@ -5274,7 +5274,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR22" t="n">
         <v>0.47</v>
@@ -5928,7 +5928,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR25" t="n">
         <v>2.04</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.33</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.83</v>
@@ -7018,7 +7018,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR30" t="n">
         <v>1.57</v>
@@ -7451,7 +7451,7 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.17</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.75</v>
@@ -8544,7 +8544,7 @@
         <v>2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR37" t="n">
         <v>1.24</v>
@@ -9198,7 +9198,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR40" t="n">
         <v>2.07</v>
@@ -9631,7 +9631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ42" t="n">
         <v>1</v>
@@ -10503,7 +10503,7 @@
         <v>3</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ46" t="n">
         <v>2</v>
@@ -10939,7 +10939,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.09</v>
@@ -11160,7 +11160,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR49" t="n">
         <v>1.21</v>
@@ -11378,7 +11378,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR50" t="n">
         <v>2.13</v>
@@ -11811,10 +11811,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR52" t="n">
         <v>1.78</v>
@@ -12032,7 +12032,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR53" t="n">
         <v>1.09</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.55</v>
@@ -12683,7 +12683,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.83</v>
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.33</v>
@@ -13122,7 +13122,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR58" t="n">
         <v>1.78</v>
@@ -13776,7 +13776,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR61" t="n">
         <v>1.57</v>
@@ -14427,7 +14427,7 @@
         <v>2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ64" t="n">
         <v>2</v>
@@ -14866,7 +14866,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR66" t="n">
         <v>1.65</v>
@@ -15299,7 +15299,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.55</v>
@@ -15738,7 +15738,7 @@
         <v>2</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR70" t="n">
         <v>1.68</v>
@@ -15953,10 +15953,10 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR71" t="n">
         <v>1.76</v>
@@ -16607,10 +16607,10 @@
         <v>0.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR74" t="n">
         <v>1.92</v>
@@ -17479,7 +17479,7 @@
         <v>0</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.33</v>
@@ -17700,7 +17700,7 @@
         <v>2</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR79" t="n">
         <v>1.78</v>
@@ -18572,7 +18572,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR83" t="n">
         <v>1.52</v>
@@ -18787,7 +18787,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.92</v>
@@ -19005,7 +19005,7 @@
         <v>2</v>
       </c>
       <c r="AP85" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ85" t="n">
         <v>2</v>
@@ -19444,7 +19444,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR87" t="n">
         <v>1.56</v>
@@ -20095,10 +20095,10 @@
         <v>1.5</v>
       </c>
       <c r="AP90" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR90" t="n">
         <v>1.84</v>
@@ -20313,7 +20313,7 @@
         <v>0.25</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.75</v>
@@ -20534,7 +20534,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR92" t="n">
         <v>2.13</v>
@@ -21839,7 +21839,7 @@
         <v>0.4</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.75</v>
@@ -22278,7 +22278,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR100" t="n">
         <v>1.58</v>
@@ -22493,7 +22493,7 @@
         <v>0.8</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.33</v>
@@ -22711,10 +22711,10 @@
         <v>0.8</v>
       </c>
       <c r="AP102" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR102" t="n">
         <v>1.68</v>
@@ -22932,7 +22932,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR103" t="n">
         <v>1.49</v>
@@ -23365,7 +23365,7 @@
         <v>1.2</v>
       </c>
       <c r="AP105" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.17</v>
@@ -23586,7 +23586,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR106" t="n">
         <v>1.17</v>
@@ -23801,10 +23801,10 @@
         <v>0.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR107" t="n">
         <v>0.93</v>
@@ -25330,7 +25330,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR114" t="n">
         <v>1.13</v>
@@ -26199,7 +26199,7 @@
         <v>1.17</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.08</v>
@@ -26417,7 +26417,7 @@
         <v>1.17</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.33</v>
@@ -26853,10 +26853,10 @@
         <v>0.17</v>
       </c>
       <c r="AP121" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR121" t="n">
         <v>1.73</v>
@@ -27071,7 +27071,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.17</v>
@@ -27292,7 +27292,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR123" t="n">
         <v>1.48</v>
@@ -27507,10 +27507,10 @@
         <v>0.67</v>
       </c>
       <c r="AP124" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR124" t="n">
         <v>1.44</v>
@@ -28164,7 +28164,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR127" t="n">
         <v>1.42</v>
@@ -28597,7 +28597,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.33</v>
@@ -30123,10 +30123,10 @@
         <v>1.29</v>
       </c>
       <c r="AP136" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR136" t="n">
         <v>1.51</v>
@@ -30344,7 +30344,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR137" t="n">
         <v>1.14</v>
@@ -30562,7 +30562,7 @@
         <v>2</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR138" t="n">
         <v>1.86</v>
@@ -30777,7 +30777,7 @@
         <v>1.75</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ139" t="n">
         <v>2</v>
@@ -30995,7 +30995,7 @@
         <v>1.14</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.17</v>
@@ -31870,7 +31870,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR144" t="n">
         <v>1.66</v>
@@ -32085,7 +32085,7 @@
         <v>1</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.09</v>
@@ -32524,7 +32524,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR147" t="n">
         <v>1.55</v>
@@ -32957,7 +32957,7 @@
         <v>1.25</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.33</v>
@@ -33175,10 +33175,10 @@
         <v>0.75</v>
       </c>
       <c r="AP150" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR150" t="n">
         <v>1.83</v>
@@ -33396,7 +33396,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ151" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
@@ -33611,7 +33611,7 @@
         <v>0.38</v>
       </c>
       <c r="AP152" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.33</v>
@@ -34704,7 +34704,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR157" t="n">
         <v>1.65</v>
@@ -34922,7 +34922,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR158" t="n">
         <v>1.54</v>
@@ -36012,7 +36012,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR163" t="n">
         <v>1.6</v>
@@ -36881,7 +36881,7 @@
         <v>2.11</v>
       </c>
       <c r="AP167" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.92</v>
@@ -37102,7 +37102,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR168" t="n">
         <v>1.09</v>
@@ -37317,10 +37317,10 @@
         <v>1.33</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR169" t="n">
         <v>1.06</v>
@@ -37753,7 +37753,7 @@
         <v>0.89</v>
       </c>
       <c r="AP171" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.75</v>
@@ -37971,7 +37971,7 @@
         <v>0.89</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ172" t="n">
         <v>1</v>
@@ -38407,7 +38407,7 @@
         <v>1.67</v>
       </c>
       <c r="AP174" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.33</v>
@@ -38625,10 +38625,10 @@
         <v>1</v>
       </c>
       <c r="AP175" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR175" t="n">
         <v>1.52</v>
@@ -39282,7 +39282,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR178" t="n">
         <v>1.43</v>
@@ -39500,7 +39500,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR179" t="n">
         <v>1.62</v>
@@ -40151,7 +40151,7 @@
         <v>1.3</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ182" t="n">
         <v>1.42</v>
@@ -40808,7 +40808,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR185" t="n">
         <v>1.19</v>
@@ -42334,7 +42334,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR192" t="n">
         <v>1.51</v>
@@ -42549,7 +42549,7 @@
         <v>1</v>
       </c>
       <c r="AP193" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ193" t="n">
         <v>1</v>
@@ -42767,10 +42767,10 @@
         <v>0.8</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR194" t="n">
         <v>1.7</v>
@@ -42985,7 +42985,7 @@
         <v>1.9</v>
       </c>
       <c r="AP195" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ195" t="n">
         <v>1.92</v>
@@ -43421,10 +43421,10 @@
         <v>0.3</v>
       </c>
       <c r="AP197" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR197" t="n">
         <v>1.1</v>
@@ -43639,7 +43639,7 @@
         <v>0.9</v>
       </c>
       <c r="AP198" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.75</v>
@@ -43860,7 +43860,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR199" t="n">
         <v>1.53</v>
@@ -45822,7 +45822,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR208" t="n">
         <v>1.48</v>
@@ -46770,6 +46770,1096 @@
       </c>
       <c r="BP212" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8206363</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>46082.45833333334</v>
+      </c>
+      <c r="F213" t="n">
+        <v>24</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>1</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>3</v>
+      </c>
+      <c r="R213" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S213" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V213" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X213" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8206450</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46082.55208333334</v>
+      </c>
+      <c r="F214" t="n">
+        <v>24</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S214" t="n">
+        <v>7</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U214" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X214" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8206454</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46082.55208333334</v>
+      </c>
+      <c r="F215" t="n">
+        <v>24</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>2</v>
+      </c>
+      <c r="J215" t="n">
+        <v>2</v>
+      </c>
+      <c r="K215" t="n">
+        <v>4</v>
+      </c>
+      <c r="L215" t="n">
+        <v>2</v>
+      </c>
+      <c r="M215" t="n">
+        <v>2</v>
+      </c>
+      <c r="N215" t="n">
+        <v>4</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['19', '29']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>['1', '24']</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R215" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S215" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U215" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V215" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X215" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8206455</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46082.55208333334</v>
+      </c>
+      <c r="F216" t="n">
+        <v>24</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" t="n">
+        <v>1</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S216" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U216" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X216" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8206452</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46082.69791666666</v>
+      </c>
+      <c r="F217" t="n">
+        <v>24</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Olympique Marseille</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Olympique Lyonnais</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" t="n">
+        <v>1</v>
+      </c>
+      <c r="L217" t="n">
+        <v>3</v>
+      </c>
+      <c r="M217" t="n">
+        <v>2</v>
+      </c>
+      <c r="N217" t="n">
+        <v>5</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['52', '81', '90+1']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>['3', '76']</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S217" t="n">
+        <v>4</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U217" t="n">
+        <v>3</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X217" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ10" t="n">
         <v>2</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.58</v>
@@ -7236,7 +7236,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR31" t="n">
         <v>0.83</v>
@@ -7672,7 +7672,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR33" t="n">
         <v>0.35</v>
@@ -8323,7 +8323,7 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.92</v>
@@ -8762,7 +8762,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR38" t="n">
         <v>1.77</v>
@@ -8977,7 +8977,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.33</v>
@@ -10942,7 +10942,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR48" t="n">
         <v>1.59</v>
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.58</v>
@@ -14212,7 +14212,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR63" t="n">
         <v>1.29</v>
@@ -14645,7 +14645,7 @@
         <v>2</v>
       </c>
       <c r="AP65" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ65" t="n">
         <v>1</v>
@@ -15084,7 +15084,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR67" t="n">
         <v>1.15</v>
@@ -16389,7 +16389,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.42</v>
@@ -19877,10 +19877,10 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR89" t="n">
         <v>0.9</v>
@@ -20316,7 +20316,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR91" t="n">
         <v>1.72</v>
@@ -20531,7 +20531,7 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.58</v>
@@ -21403,7 +21403,7 @@
         <v>0</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.33</v>
@@ -21842,7 +21842,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR98" t="n">
         <v>1.8</v>
@@ -24894,7 +24894,7 @@
         <v>2</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR112" t="n">
         <v>1.81</v>
@@ -25109,7 +25109,7 @@
         <v>0.83</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.55</v>
@@ -25548,7 +25548,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR115" t="n">
         <v>1.64</v>
@@ -25763,7 +25763,7 @@
         <v>0.17</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.83</v>
@@ -28382,7 +28382,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR128" t="n">
         <v>1.64</v>
@@ -28815,7 +28815,7 @@
         <v>1.86</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.92</v>
@@ -29251,7 +29251,7 @@
         <v>1.43</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.33</v>
@@ -29472,7 +29472,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR133" t="n">
         <v>1.38</v>
@@ -32088,7 +32088,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR145" t="n">
         <v>1.82</v>
@@ -33832,7 +33832,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR153" t="n">
         <v>1.56</v>
@@ -34047,7 +34047,7 @@
         <v>1</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.08</v>
@@ -34483,7 +34483,7 @@
         <v>1.63</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.42</v>
@@ -35573,7 +35573,7 @@
         <v>0.89</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.08</v>
@@ -36666,7 +36666,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR166" t="n">
         <v>1.54</v>
@@ -37099,7 +37099,7 @@
         <v>0.44</v>
       </c>
       <c r="AP168" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.58</v>
@@ -37756,7 +37756,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR171" t="n">
         <v>1.57</v>
@@ -40805,7 +40805,7 @@
         <v>1.5</v>
       </c>
       <c r="AP185" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.38</v>
@@ -41026,7 +41026,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR186" t="n">
         <v>1.44</v>
@@ -41895,7 +41895,7 @@
         <v>1.6</v>
       </c>
       <c r="AP190" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.33</v>
@@ -43642,7 +43642,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ198" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR198" t="n">
         <v>1.46</v>
@@ -44296,7 +44296,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR201" t="n">
         <v>1.63</v>
@@ -44729,7 +44729,7 @@
         <v>0.36</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ203" t="n">
         <v>0.33</v>
@@ -45601,7 +45601,7 @@
         <v>0.6</v>
       </c>
       <c r="AP207" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.55</v>
@@ -46476,7 +46476,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ211" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR211" t="n">
         <v>1.51</v>
@@ -47860,6 +47860,442 @@
       </c>
       <c r="BP217" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8206457</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46087.69791666666</v>
+      </c>
+      <c r="F218" t="n">
+        <v>25</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1</v>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="n">
+        <v>3</v>
+      </c>
+      <c r="N218" t="n">
+        <v>4</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>['27', '55', '73']</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R218" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="S218" t="n">
+        <v>6</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U218" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V218" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X218" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8206456</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46088.54166666666</v>
+      </c>
+      <c r="F219" t="n">
+        <v>25</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Angers SCO</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R219" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S219" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U219" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V219" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X219" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France Ligue 1_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ16" t="n">
         <v>1</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ23" t="n">
         <v>2</v>
@@ -6582,7 +6582,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR28" t="n">
         <v>1.59</v>
@@ -10724,7 +10724,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR47" t="n">
         <v>1.53</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.75</v>
@@ -12904,7 +12904,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR57" t="n">
         <v>0.79</v>
@@ -16171,7 +16171,7 @@
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.33</v>
@@ -17264,7 +17264,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR77" t="n">
         <v>1.94</v>
@@ -19659,7 +19659,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.33</v>
@@ -20970,7 +20970,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR94" t="n">
         <v>1.13</v>
@@ -22057,7 +22057,7 @@
         <v>0.8</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.55</v>
@@ -24458,7 +24458,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR110" t="n">
         <v>1.38</v>
@@ -25545,7 +25545,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.92</v>
@@ -28600,7 +28600,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR129" t="n">
         <v>1.83</v>
@@ -29033,7 +29033,7 @@
         <v>1</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ131" t="n">
         <v>1</v>
@@ -32303,7 +32303,7 @@
         <v>2</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.92</v>
@@ -34919,7 +34919,7 @@
         <v>0.5</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.58</v>
@@ -35140,7 +35140,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR159" t="n">
         <v>1.27</v>
@@ -38410,7 +38410,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR174" t="n">
         <v>1.49</v>
@@ -39497,7 +39497,7 @@
         <v>0.22</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ179" t="n">
         <v>0.58</v>
@@ -41898,7 +41898,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR190" t="n">
         <v>2.36</v>
@@ -44078,7 +44078,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR200" t="n">
         <v>1.53</v>
@@ -44511,7 +44511,7 @@
         <v>1.09</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.08</v>
@@ -48296,6 +48296,442 @@
       </c>
       <c r="BP219" t="n">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8206458</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46088.625</v>
+      </c>
+      <c r="F220" t="n">
+        <v>25</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S220" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U220" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V220" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X220" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>8206460</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46088.71180555555</v>
+      </c>
+      <c r="F221" t="n">
+        <v>25</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Olympique Marseille</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>1</v>
+      </c>
+      <c r="N221" t="n">
+        <v>1</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R221" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S221" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U221" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V221" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X221" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
